--- a/astro-site/public/dl/guia-panaderia-obrador/cronograma-apertura-gantt.xlsx
+++ b/astro-site/public/dl/guia-panaderia-obrador/cronograma-apertura-gantt.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gantt apertura" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Gantt apertura'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -448,7 +450,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -471,6 +473,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -534,11 +537,6 @@
           <t>■</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Cierra el modelo</t>
@@ -566,10 +564,6 @@
           <t>■</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Killer: verifica humos ANTES</t>
@@ -587,16 +581,11 @@
           <t>Tú + abogado</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Cláusula salida si licencia denegada</t>
@@ -614,7 +603,6 @@
           <t>Ingeniero</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>■</t>
@@ -625,9 +613,6 @@
           <t>■</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>4-7K€ orientativo</t>
@@ -645,8 +630,6 @@
           <t>Gestor</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>■</t>
@@ -657,8 +640,6 @@
           <t>■</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>60-120 días resolución</t>
@@ -676,8 +657,6 @@
           <t>Gestor</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>■</t>
@@ -688,8 +667,6 @@
           <t>■</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Tras licencia obra</t>
@@ -707,16 +684,11 @@
           <t>Tú</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Plazo 4-8 semanas</t>
@@ -734,9 +706,6 @@
           <t>Constructor</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>■</t>
@@ -747,8 +716,6 @@
           <t>■</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -761,17 +728,11 @@
           <t>Instalador</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -784,17 +745,11 @@
           <t>Proveedor</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -807,17 +762,11 @@
           <t>Tú + asesor</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -830,16 +779,11 @@
           <t>Tú + RRHH</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>■</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Panadero clave: 30-45 días</t>
@@ -857,9 +801,6 @@
           <t>Diseñador</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>■</t>
@@ -870,8 +811,6 @@
           <t>■</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -884,11 +823,6 @@
           <t>Panadero</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>■</t>
@@ -911,11 +845,6 @@
           <t>Equipo</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>■</t>
@@ -938,11 +867,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>★</t>
@@ -958,6 +882,15 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>